--- a/config/listing_master.xlsx
+++ b/config/listing_master.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listing Master" sheetId="1" r:id="Rdfba0c2266e846f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="2" r:id="R3c532019a4484924"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listing Master" sheetId="1" r:id="R105f7d8b9e874b01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="2" r:id="R4897417f2cbb418e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -63,7 +63,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="15">
+  <x:borders count="22">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -186,11 +186,79 @@
         <x:color rgb="FF9FBAD0"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE2E8F0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE2E8F0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE2E8F0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE2E8F0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE2E8F0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE2E8F0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE2E8F0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE2E8F0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE2E8F0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -281,6 +349,70 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -569,146 +701,2138 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="25"/>
-      <x:c r="B2" s="26"/>
-      <x:c r="C2" s="26"/>
-      <x:c r="D2" s="26"/>
-      <x:c r="E2" s="26"/>
-      <x:c r="F2" s="26"/>
-      <x:c r="G2" s="26"/>
-      <x:c r="H2" s="26"/>
-      <x:c r="I2" s="26"/>
-      <x:c r="J2" s="26"/>
-      <x:c r="K2" s="26"/>
-      <x:c r="L2" s="26"/>
-      <x:c r="M2" s="26"/>
-      <x:c r="N2" s="28"/>
-      <x:c r="O2" s="26"/>
-      <x:c r="P2" s="26"/>
-      <x:c r="Q2" s="26"/>
-      <x:c r="R2" s="26"/>
-      <x:c r="S2" s="26"/>
-      <x:c r="T2" s="27"/>
+      <x:c r="A2" s="58" t="str">
+        <x:v>LOWES_WB20V16LM</x:v>
+      </x:c>
+      <x:c r="B2" s="47" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C2" s="47" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D2" s="47" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E2" s="47" t="str">
+        <x:v>Lawn Mower</x:v>
+      </x:c>
+      <x:c r="F2" s="48" t="str">
+        <x:v>WB20V16LM</x:v>
+      </x:c>
+      <x:c r="G2" s="48" t="str"/>
+      <x:c r="H2" s="48" t="str">
+        <x:v>5014394923</x:v>
+      </x:c>
+      <x:c r="I2" s="47" t="str">
+        <x:v>20 Volt, 16-in Push Battery Walk Mower with  (2) 4 Ah Batteries Included</x:v>
+      </x:c>
+      <x:c r="J2" s="61" t="str">
+        <x:v>https://www.lowes.com/pd/Wild-Badger-Power-20-volt-16-in-Push-Cordless-Lawn-Mower-4-Ah-Battery-Charger-Included/5014394923</x:v>
+      </x:c>
+      <x:c r="K2" s="47" t="str"/>
+      <x:c r="L2" s="47" t="str"/>
+      <x:c r="M2" s="47" t="str"/>
+      <x:c r="N2" s="48" t="str"/>
+      <x:c r="O2" s="47" t="str"/>
+      <x:c r="P2" s="47" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q2" s="47" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R2" s="47" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S2" s="47" t="str"/>
+      <x:c r="T2" s="64" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="N3" s="29"/>
+      <x:c r="A3" s="59" t="str">
+        <x:v>LOWES_WB40V18PLM</x:v>
+      </x:c>
+      <x:c r="B3" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C3" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D3" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E3" s="51" t="str">
+        <x:v>Lawn Mower</x:v>
+      </x:c>
+      <x:c r="F3" s="52" t="str">
+        <x:v>WB40V18PLM</x:v>
+      </x:c>
+      <x:c r="G3" s="52" t="str"/>
+      <x:c r="H3" s="52" t="str">
+        <x:v>5014466573</x:v>
+      </x:c>
+      <x:c r="I3" s="56" t="str">
+        <x:v>Brushless 40-volt, 18-in Push Battery Walk Mower with  (1) 4 Ah Battery Included</x:v>
+      </x:c>
+      <x:c r="J3" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Wild-Badger-Power-40-Volt-40-volt-18-in-Push-Cordless-Lawn-Mower-4-Ah-Battery-Charger-Included/5014466573</x:v>
+      </x:c>
+      <x:c r="K3" s="51" t="str"/>
+      <x:c r="L3" s="51" t="str"/>
+      <x:c r="M3" s="51" t="str"/>
+      <x:c r="N3" s="52" t="str"/>
+      <x:c r="O3" s="51" t="str"/>
+      <x:c r="P3" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q3" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R3" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S3" s="51" t="str"/>
+      <x:c r="T3" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="N4" s="29"/>
+      <x:c r="A4" s="59" t="str">
+        <x:v>LOWES_WB40V14PLM</x:v>
+      </x:c>
+      <x:c r="B4" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C4" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D4" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E4" s="51" t="str">
+        <x:v>Lawn Mower</x:v>
+      </x:c>
+      <x:c r="F4" s="52" t="str">
+        <x:v>WB40V14PLM</x:v>
+      </x:c>
+      <x:c r="G4" s="52" t="str"/>
+      <x:c r="H4" s="52" t="str">
+        <x:v>6595295</x:v>
+      </x:c>
+      <x:c r="I4" s="56" t="str"/>
+      <x:c r="J4" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Wild-Badger-Power-Cordless-40-volt-14-in-Cordless-Push-Lawn-Mower-4-Ah-1-Battery-and-Charger-Included/6595295</x:v>
+      </x:c>
+      <x:c r="K4" s="51" t="str"/>
+      <x:c r="L4" s="51" t="str"/>
+      <x:c r="M4" s="51" t="str"/>
+      <x:c r="N4" s="52" t="str"/>
+      <x:c r="O4" s="51" t="str"/>
+      <x:c r="P4" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q4" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R4" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S4" s="51" t="str"/>
+      <x:c r="T4" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="N5" s="29"/>
+      <x:c r="A5" s="59" t="str">
+        <x:v>LOWES_WB20VPS</x:v>
+      </x:c>
+      <x:c r="B5" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C5" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D5" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E5" s="51" t="str">
+        <x:v>Pole Saws</x:v>
+      </x:c>
+      <x:c r="F5" s="52" t="str">
+        <x:v>WB20VPS</x:v>
+      </x:c>
+      <x:c r="G5" s="52" t="str"/>
+      <x:c r="H5" s="52" t="str">
+        <x:v>5001889319</x:v>
+      </x:c>
+      <x:c r="I5" s="56" t="str">
+        <x:v>20 Volt 20-volt 8.0-in 2.0 Ah Battery Pole Saw Battery Included , Charger Included</x:v>
+      </x:c>
+      <x:c r="J5" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Badger-20-Volt-Lithium-Ion-Pole-Saw-Extendable-to-Over-6-ft-with-2-0-Ah-Battery-and-Charger/5001889319?idProductFound=false&amp;idExtracted=true</x:v>
+      </x:c>
+      <x:c r="K5" s="51" t="str"/>
+      <x:c r="L5" s="51" t="str"/>
+      <x:c r="M5" s="51" t="str"/>
+      <x:c r="N5" s="52" t="str"/>
+      <x:c r="O5" s="51" t="str"/>
+      <x:c r="P5" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q5" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R5" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S5" s="51" t="str"/>
+      <x:c r="T5" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="N6" s="29"/>
+      <x:c r="A6" s="59" t="str">
+        <x:v>LOWES_RMA1202L20VU</x:v>
+      </x:c>
+      <x:c r="B6" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C6" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D6" s="51" t="str">
+        <x:v>SUNSEEKER</x:v>
+      </x:c>
+      <x:c r="E6" s="51" t="str">
+        <x:v>Robot Mower</x:v>
+      </x:c>
+      <x:c r="F6" s="52" t="str">
+        <x:v>RMA1202L20VU</x:v>
+      </x:c>
+      <x:c r="G6" s="52" t="str"/>
+      <x:c r="H6" s="52" t="str">
+        <x:v>5014696123</x:v>
+      </x:c>
+      <x:c r="I6" s="56" t="str">
+        <x:v>L22 Robotic Lawn Mower (1_SLASH_8 to 1_SLASH_4 acre)</x:v>
+      </x:c>
+      <x:c r="J6" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Sunseeker-Robotic-Mower-Robotic-Lawn-Mower-Up-To-1-4-Acre/5014696123</x:v>
+      </x:c>
+      <x:c r="K6" s="51" t="str"/>
+      <x:c r="L6" s="51" t="str"/>
+      <x:c r="M6" s="51" t="str"/>
+      <x:c r="N6" s="52" t="str"/>
+      <x:c r="O6" s="51" t="str"/>
+      <x:c r="P6" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q6" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R6" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S6" s="51" t="str"/>
+      <x:c r="T6" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="N7" s="29"/>
+      <x:c r="A7" s="59" t="str">
+        <x:v>LOWES_ORIONX7</x:v>
+      </x:c>
+      <x:c r="B7" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C7" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D7" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E7" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F7" s="52" t="str">
+        <x:v>ORIONX7</x:v>
+      </x:c>
+      <x:c r="G7" s="52" t="str">
+        <x:v>X7</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="str">
+        <x:v>7196963</x:v>
+      </x:c>
+      <x:c r="I7" s="56" t="str">
+        <x:v>Sunseeker X7 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J7" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Sunseeker-X7-Robotic-Lawn-Mower-with-GPS-Assisted-Navigation-1-2-acre-to-1-acre/5016678663</x:v>
+      </x:c>
+      <x:c r="K7" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L7" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M7" s="51" t="str"/>
+      <x:c r="N7" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O7" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P7" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q7" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R7" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S7" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T7" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="N8" s="29"/>
+      <x:c r="A8" s="59" t="str">
+        <x:v>LOWES_SKRMV3</x:v>
+      </x:c>
+      <x:c r="B8" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C8" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D8" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E8" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F8" s="52" t="str">
+        <x:v>SKRMV3</x:v>
+      </x:c>
+      <x:c r="G8" s="52" t="str">
+        <x:v>V3</x:v>
+      </x:c>
+      <x:c r="H8" s="52" t="str">
+        <x:v>7196962</x:v>
+      </x:c>
+      <x:c r="I8" s="56" t="str">
+        <x:v>Sunseeker V3 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J8" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Sunseeker-V3-Robotic-Lawn-Mower-with-GPS-Assisted-Navigation-Up-to-1-8-acre/5016678667</x:v>
+      </x:c>
+      <x:c r="K8" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L8" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M8" s="51" t="str"/>
+      <x:c r="N8" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O8" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P8" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q8" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R8" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S8" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T8" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="N9" s="29"/>
+      <x:c r="A9" s="59" t="str">
+        <x:v>LOWES_SKRMX3PLUS</x:v>
+      </x:c>
+      <x:c r="B9" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C9" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D9" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E9" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F9" s="52" t="str">
+        <x:v>SKRMX3PLUS</x:v>
+      </x:c>
+      <x:c r="G9" s="52" t="str">
+        <x:v>X3PLUS</x:v>
+      </x:c>
+      <x:c r="H9" s="52" t="str">
+        <x:v>7196961</x:v>
+      </x:c>
+      <x:c r="I9" s="56" t="str">
+        <x:v>Sunseeker X3PLUS Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J9" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Sunseeker-X3-PLUS-Robotic-Lawn-Mower-with-GPS-Assisted-Navigation-1-4-acre-to-1-2-acre/5016678665</x:v>
+      </x:c>
+      <x:c r="K9" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L9" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M9" s="51" t="str"/>
+      <x:c r="N9" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O9" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P9" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q9" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R9" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S9" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T9" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="N10" s="29"/>
+      <x:c r="A10" s="59" t="str">
+        <x:v>LOWES_SKRMX5</x:v>
+      </x:c>
+      <x:c r="B10" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C10" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D10" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E10" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F10" s="52" t="str">
+        <x:v>SKRMX5</x:v>
+      </x:c>
+      <x:c r="G10" s="52" t="str">
+        <x:v>X5</x:v>
+      </x:c>
+      <x:c r="H10" s="52" t="str">
+        <x:v>9714237</x:v>
+      </x:c>
+      <x:c r="I10" s="56" t="str">
+        <x:v>Sunseeker X5 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J10" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Sunseeker-Robotic-Lawn-Mower-with-GPS-Assisted-Navigation-1-2-to-1-acre/5020541633</x:v>
+      </x:c>
+      <x:c r="K10" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L10" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M10" s="51" t="str"/>
+      <x:c r="N10" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O10" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P10" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q10" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R10" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="S10" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T10" s="62" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="N11" s="29"/>
+      <x:c r="A11" s="59" t="str">
+        <x:v>LOWES_SKRMS4</x:v>
+      </x:c>
+      <x:c r="B11" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C11" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D11" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E11" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F11" s="52" t="str">
+        <x:v>SKRMS4</x:v>
+      </x:c>
+      <x:c r="G11" s="52" t="str">
+        <x:v>S4</x:v>
+      </x:c>
+      <x:c r="H11" s="52" t="str">
+        <x:v>9714238</x:v>
+      </x:c>
+      <x:c r="I11" s="56" t="str">
+        <x:v>Sunseeker S4 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J11" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Sunseeker-Robotic-Lawn-Mower-with-GPS-Assisted-Navigation-1-8-to-1-4-acre/5020541631</x:v>
+      </x:c>
+      <x:c r="K11" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L11" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M11" s="51" t="str"/>
+      <x:c r="N11" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O11" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P11" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q11" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R11" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="S11" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T11" s="62" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="N12" s="29"/>
+      <x:c r="A12" s="59" t="str">
+        <x:v>LOWES_WB20VTRSBL</x:v>
+      </x:c>
+      <x:c r="B12" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C12" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D12" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E12" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F12" s="52" t="str">
+        <x:v>WB20VTRSBL</x:v>
+      </x:c>
+      <x:c r="G12" s="52" t="str"/>
+      <x:c r="H12" s="52" t="str">
+        <x:v>5014472275</x:v>
+      </x:c>
+      <x:c r="I12" s="56" t="str">
+        <x:v>20 Volt 20-volt Cordless Battery String Trimmer and Leaf Blower and Combo Kit 2 Ah (Battery Included) (Charger Included)</x:v>
+      </x:c>
+      <x:c r="J12" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Wild-Badger-Power-20-Volt-2-Piece-20-volt-Cordless-Power-Equipment-Combo-Kit/5014472275</x:v>
+      </x:c>
+      <x:c r="K12" s="51" t="str"/>
+      <x:c r="L12" s="51" t="str"/>
+      <x:c r="M12" s="51" t="str"/>
+      <x:c r="N12" s="52" t="str"/>
+      <x:c r="O12" s="51" t="str"/>
+      <x:c r="P12" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q12" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R12" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S12" s="51" t="str"/>
+      <x:c r="T12" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="N13" s="29"/>
+      <x:c r="A13" s="59" t="str">
+        <x:v>LOWES_WB20VTAB</x:v>
+      </x:c>
+      <x:c r="B13" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C13" s="51" t="str">
+        <x:v>LOWES</x:v>
+      </x:c>
+      <x:c r="D13" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E13" s="51" t="str">
+        <x:v>String Trimmers</x:v>
+      </x:c>
+      <x:c r="F13" s="52" t="str">
+        <x:v>WB20VTAB</x:v>
+      </x:c>
+      <x:c r="G13" s="52" t="str"/>
+      <x:c r="H13" s="52" t="str">
+        <x:v>5001743443</x:v>
+      </x:c>
+      <x:c r="I13" s="56" t="str">
+        <x:v>20-volt 12-in Straight Shaft Battery String Trimmer Edger Conversion Capable 2 Ah (Battery Included) (Charger Included)</x:v>
+      </x:c>
+      <x:c r="J13" s="62" t="str">
+        <x:v>https://www.lowes.com/pd/Badger-Badger-20-Volt-Lithium-Ion-Sting-Trimmer-Edger-and-Sweeper-Blower-with-2-0-Ah-Battery-and-Charger/5001743443?idProductFound=false&amp;idExtracted=true</x:v>
+      </x:c>
+      <x:c r="K13" s="51" t="str"/>
+      <x:c r="L13" s="51" t="str"/>
+      <x:c r="M13" s="51" t="str"/>
+      <x:c r="N13" s="52" t="str"/>
+      <x:c r="O13" s="51" t="str"/>
+      <x:c r="P13" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q13" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R13" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S13" s="51" t="str"/>
+      <x:c r="T13" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="N14" s="29"/>
+      <x:c r="A14" s="59" t="str">
+        <x:v>THD_WB53CULT</x:v>
+      </x:c>
+      <x:c r="B14" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C14" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D14" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E14" s="51" t="str">
+        <x:v>Garden Tiller</x:v>
+      </x:c>
+      <x:c r="F14" s="52" t="str">
+        <x:v>WB53CULT</x:v>
+      </x:c>
+      <x:c r="G14" s="52" t="str"/>
+      <x:c r="H14" s="52" t="str">
+        <x:v>337271637</x:v>
+      </x:c>
+      <x:c r="I14" s="56" t="str">
+        <x:v>15 in. 53cc 2-Cycle Gas Powered Push Garden Tiller Cultivator</x:v>
+      </x:c>
+      <x:c r="J14" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/337271637</x:v>
+      </x:c>
+      <x:c r="K14" s="51" t="str"/>
+      <x:c r="L14" s="51" t="str"/>
+      <x:c r="M14" s="51" t="str"/>
+      <x:c r="N14" s="52" t="str"/>
+      <x:c r="O14" s="51" t="str"/>
+      <x:c r="P14" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q14" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R14" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S14" s="51" t="str"/>
+      <x:c r="T14" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="N15" s="29"/>
+      <x:c r="A15" s="59" t="str">
+        <x:v>THD_WBBPBL43</x:v>
+      </x:c>
+      <x:c r="B15" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C15" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D15" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E15" s="51" t="str">
+        <x:v>Leaf Blower</x:v>
+      </x:c>
+      <x:c r="F15" s="52" t="str">
+        <x:v>WBBPBL43</x:v>
+      </x:c>
+      <x:c r="G15" s="52" t="str"/>
+      <x:c r="H15" s="52" t="str">
+        <x:v>314742167</x:v>
+      </x:c>
+      <x:c r="I15" s="56" t="str">
+        <x:v>Leaf Blower Backpack, 43cc Gas Strong Air Flow 650 CFM 152 MPH, Light Weight 17.4 lbs.</x:v>
+      </x:c>
+      <x:c r="J15" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/314742167</x:v>
+      </x:c>
+      <x:c r="K15" s="51" t="str"/>
+      <x:c r="L15" s="51" t="str"/>
+      <x:c r="M15" s="51" t="str"/>
+      <x:c r="N15" s="52" t="str"/>
+      <x:c r="O15" s="51" t="str"/>
+      <x:c r="P15" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q15" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R15" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S15" s="51" t="str"/>
+      <x:c r="T15" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="N16" s="29"/>
+      <x:c r="A16" s="59" t="str">
+        <x:v>THD_WB52CCBPB</x:v>
+      </x:c>
+      <x:c r="B16" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C16" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D16" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E16" s="51" t="str">
+        <x:v>Leaf Blower</x:v>
+      </x:c>
+      <x:c r="F16" s="52" t="str">
+        <x:v>WB52CCBPB</x:v>
+      </x:c>
+      <x:c r="G16" s="52" t="str"/>
+      <x:c r="H16" s="52" t="str">
+        <x:v>325379597</x:v>
+      </x:c>
+      <x:c r="I16" s="56" t="str">
+        <x:v>Gas 53cc Backpack Blower 175MPH 855CFM</x:v>
+      </x:c>
+      <x:c r="J16" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/325379597</x:v>
+      </x:c>
+      <x:c r="K16" s="51" t="str"/>
+      <x:c r="L16" s="51" t="str"/>
+      <x:c r="M16" s="51" t="str"/>
+      <x:c r="N16" s="52" t="str"/>
+      <x:c r="O16" s="51" t="str"/>
+      <x:c r="P16" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q16" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R16" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S16" s="51" t="str"/>
+      <x:c r="T16" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="N17" s="29"/>
+      <x:c r="A17" s="59" t="str">
+        <x:v>THD_SKRMS4</x:v>
+      </x:c>
+      <x:c r="B17" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C17" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D17" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E17" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F17" s="52" t="str">
+        <x:v>SKRMS4</x:v>
+      </x:c>
+      <x:c r="G17" s="52" t="str">
+        <x:v>S4</x:v>
+      </x:c>
+      <x:c r="H17" s="52" t="str">
+        <x:v>343186124</x:v>
+      </x:c>
+      <x:c r="I17" s="56" t="str">
+        <x:v>Sunseeker S4 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J17" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/343186124</x:v>
+      </x:c>
+      <x:c r="K17" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L17" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M17" s="51" t="str"/>
+      <x:c r="N17" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O17" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P17" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q17" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R17" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S17" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T17" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="N18" s="29"/>
+      <x:c r="A18" s="59" t="str">
+        <x:v>THD_SKRMV3</x:v>
+      </x:c>
+      <x:c r="B18" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C18" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D18" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E18" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F18" s="52" t="str">
+        <x:v>SKRMV3</x:v>
+      </x:c>
+      <x:c r="G18" s="52" t="str">
+        <x:v>V3</x:v>
+      </x:c>
+      <x:c r="H18" s="52" t="str">
+        <x:v>336617178</x:v>
+      </x:c>
+      <x:c r="I18" s="56" t="str">
+        <x:v>Sunseeker V3 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J18" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/336617178</x:v>
+      </x:c>
+      <x:c r="K18" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L18" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M18" s="51" t="str"/>
+      <x:c r="N18" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O18" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P18" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q18" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R18" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="S18" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T18" s="62" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="N19" s="29"/>
+      <x:c r="A19" s="59" t="str">
+        <x:v>THD_SKRMX5</x:v>
+      </x:c>
+      <x:c r="B19" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C19" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D19" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E19" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F19" s="52" t="str">
+        <x:v>SKRMX5</x:v>
+      </x:c>
+      <x:c r="G19" s="52" t="str">
+        <x:v>X5</x:v>
+      </x:c>
+      <x:c r="H19" s="52" t="str">
+        <x:v>335471654</x:v>
+      </x:c>
+      <x:c r="I19" s="56" t="str">
+        <x:v>Sunseeker X5 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J19" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/335471654</x:v>
+      </x:c>
+      <x:c r="K19" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L19" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M19" s="51" t="str"/>
+      <x:c r="N19" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O19" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P19" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q19" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R19" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="S19" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T19" s="62" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="N20" s="29"/>
+      <x:c r="A20" s="59" t="str">
+        <x:v>THD_SKRMX3PLUS</x:v>
+      </x:c>
+      <x:c r="B20" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C20" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D20" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E20" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F20" s="52" t="str">
+        <x:v>SKRMX3PLUS</x:v>
+      </x:c>
+      <x:c r="G20" s="52" t="str">
+        <x:v>X3PLUS</x:v>
+      </x:c>
+      <x:c r="H20" s="52" t="str">
+        <x:v>336272752</x:v>
+      </x:c>
+      <x:c r="I20" s="56" t="str">
+        <x:v>Sunseeker X3PLUS Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J20" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/336272752</x:v>
+      </x:c>
+      <x:c r="K20" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L20" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M20" s="51" t="str"/>
+      <x:c r="N20" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O20" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P20" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q20" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R20" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="S20" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T20" s="62" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="N21" s="29"/>
+      <x:c r="A21" s="59" t="str">
+        <x:v>THD_ORIONX7</x:v>
+      </x:c>
+      <x:c r="B21" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C21" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D21" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E21" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F21" s="52" t="str">
+        <x:v>ORIONX7</x:v>
+      </x:c>
+      <x:c r="G21" s="52" t="str">
+        <x:v>X7</x:v>
+      </x:c>
+      <x:c r="H21" s="52" t="str">
+        <x:v>337020714</x:v>
+      </x:c>
+      <x:c r="I21" s="56" t="str">
+        <x:v>Sunseeker X7 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J21" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/337020714</x:v>
+      </x:c>
+      <x:c r="K21" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L21" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M21" s="51" t="str"/>
+      <x:c r="N21" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O21" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P21" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q21" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R21" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="S21" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T21" s="62" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="N22" s="29"/>
+      <x:c r="A22" s="59" t="str">
+        <x:v>THD_WBP31BCF</x:v>
+      </x:c>
+      <x:c r="B22" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C22" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D22" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E22" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F22" s="52" t="str">
+        <x:v>WBP31BCF</x:v>
+      </x:c>
+      <x:c r="G22" s="52" t="str"/>
+      <x:c r="H22" s="52" t="str">
+        <x:v>311424786</x:v>
+      </x:c>
+      <x:c r="I22" s="56" t="str">
+        <x:v>31cc String Trimmer 4-Stroke 31cc Brush Cutter Blade Gas Shoulder Strap String Trimmer Rubber Handle</x:v>
+      </x:c>
+      <x:c r="J22" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/311424786</x:v>
+      </x:c>
+      <x:c r="K22" s="51" t="str"/>
+      <x:c r="L22" s="51" t="str"/>
+      <x:c r="M22" s="51" t="str"/>
+      <x:c r="N22" s="52" t="str"/>
+      <x:c r="O22" s="51" t="str"/>
+      <x:c r="P22" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q22" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R22" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S22" s="51" t="str"/>
+      <x:c r="T22" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="N23" s="29"/>
+      <x:c r="A23" s="59" t="str">
+        <x:v>THD_WBP52BCI</x:v>
+      </x:c>
+      <x:c r="B23" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C23" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D23" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E23" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F23" s="52" t="str">
+        <x:v>WBP52BCI</x:v>
+      </x:c>
+      <x:c r="G23" s="52" t="str"/>
+      <x:c r="H23" s="52" t="str">
+        <x:v>311424784</x:v>
+      </x:c>
+      <x:c r="I23" s="56" t="str">
+        <x:v>52 cc Gas 2-Stroke 2-in-1 Brush Cutter and String Hand Held Trimmer</x:v>
+      </x:c>
+      <x:c r="J23" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/311424784</x:v>
+      </x:c>
+      <x:c r="K23" s="51" t="str"/>
+      <x:c r="L23" s="51" t="str"/>
+      <x:c r="M23" s="51" t="str"/>
+      <x:c r="N23" s="52" t="str"/>
+      <x:c r="O23" s="51" t="str"/>
+      <x:c r="P23" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q23" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R23" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S23" s="51" t="str"/>
+      <x:c r="T23" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="N24" s="29"/>
+      <x:c r="A24" s="59" t="str">
+        <x:v>THD_WBPMT26TS</x:v>
+      </x:c>
+      <x:c r="B24" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C24" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D24" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E24" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F24" s="52" t="str">
+        <x:v>WBPMT26TS</x:v>
+      </x:c>
+      <x:c r="G24" s="52" t="str"/>
+      <x:c r="H24" s="52" t="str">
+        <x:v>342972128</x:v>
+      </x:c>
+      <x:c r="I24" s="56" t="str">
+        <x:v>26cc 4-in-1 Full Crank 2-Stroke Gas Straight Shaft Multi-Function String Trimmer with Pole Saw Attachment and Spool</x:v>
+      </x:c>
+      <x:c r="J24" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/342972128</x:v>
+      </x:c>
+      <x:c r="K24" s="51" t="str"/>
+      <x:c r="L24" s="51" t="str"/>
+      <x:c r="M24" s="51" t="str"/>
+      <x:c r="N24" s="52" t="str"/>
+      <x:c r="O24" s="51" t="str"/>
+      <x:c r="P24" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q24" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R24" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S24" s="51" t="str"/>
+      <x:c r="T24" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="N25" s="29"/>
+      <x:c r="A25" s="59" t="str">
+        <x:v>THD_WBP31TS</x:v>
+      </x:c>
+      <x:c r="B25" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C25" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D25" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E25" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F25" s="52" t="str">
+        <x:v>WBP31TS</x:v>
+      </x:c>
+      <x:c r="G25" s="52" t="str"/>
+      <x:c r="H25" s="52" t="str">
+        <x:v>342971818</x:v>
+      </x:c>
+      <x:c r="I25" s="56" t="str">
+        <x:v>31cc 17 in. 4-Stroke 31cc Gas Straight Shaft String Trimmer with Brush Cutter Blade, Rubber Handle and Extra Spool</x:v>
+      </x:c>
+      <x:c r="J25" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/342971818</x:v>
+      </x:c>
+      <x:c r="K25" s="51" t="str"/>
+      <x:c r="L25" s="51" t="str"/>
+      <x:c r="M25" s="51" t="str"/>
+      <x:c r="N25" s="52" t="str"/>
+      <x:c r="O25" s="51" t="str"/>
+      <x:c r="P25" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q25" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R25" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S25" s="51" t="str"/>
+      <x:c r="T25" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="N26" s="29"/>
+      <x:c r="A26" s="59" t="str">
+        <x:v>THD_WB26GTC</x:v>
+      </x:c>
+      <x:c r="B26" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C26" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D26" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E26" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F26" s="52" t="str">
+        <x:v>WB26GTC</x:v>
+      </x:c>
+      <x:c r="G26" s="52" t="str"/>
+      <x:c r="H26" s="52" t="str">
+        <x:v>325368686</x:v>
+      </x:c>
+      <x:c r="I26" s="56" t="str">
+        <x:v>15in Cutting Width Gas 26cc Grass Trimmer with 60° Curved Shaft</x:v>
+      </x:c>
+      <x:c r="J26" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/325368686</x:v>
+      </x:c>
+      <x:c r="K26" s="51" t="str"/>
+      <x:c r="L26" s="51" t="str"/>
+      <x:c r="M26" s="51" t="str"/>
+      <x:c r="N26" s="52" t="str"/>
+      <x:c r="O26" s="51" t="str"/>
+      <x:c r="P26" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q26" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R26" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S26" s="51" t="str"/>
+      <x:c r="T26" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="N27" s="29"/>
+      <x:c r="A27" s="59" t="str">
+        <x:v>THD_WBP52TS</x:v>
+      </x:c>
+      <x:c r="B27" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C27" s="51" t="str">
+        <x:v>THD</x:v>
+      </x:c>
+      <x:c r="D27" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E27" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F27" s="52" t="str">
+        <x:v>WBP52TS</x:v>
+      </x:c>
+      <x:c r="G27" s="52" t="str"/>
+      <x:c r="H27" s="52" t="str">
+        <x:v>342971888</x:v>
+      </x:c>
+      <x:c r="I27" s="56" t="str">
+        <x:v>52 cc 2-in-1 2-Stroke Gas Straight Shaft Brush Cutter and String Hand Held Trimmer with Extra Spool</x:v>
+      </x:c>
+      <x:c r="J27" s="62" t="str">
+        <x:v>https://www.homedepot.com/p/342971888</x:v>
+      </x:c>
+      <x:c r="K27" s="51" t="str"/>
+      <x:c r="L27" s="51" t="str"/>
+      <x:c r="M27" s="51" t="str"/>
+      <x:c r="N27" s="52" t="str"/>
+      <x:c r="O27" s="51" t="str"/>
+      <x:c r="P27" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q27" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R27" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S27" s="51" t="str"/>
+      <x:c r="T27" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="N28" s="29"/>
+      <x:c r="A28" s="59" t="str">
+        <x:v>WALMART_WB53CULT</x:v>
+      </x:c>
+      <x:c r="B28" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C28" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D28" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E28" s="51" t="str">
+        <x:v>Garden Tiller</x:v>
+      </x:c>
+      <x:c r="F28" s="52" t="str">
+        <x:v>WB53CULT</x:v>
+      </x:c>
+      <x:c r="G28" s="52" t="str"/>
+      <x:c r="H28" s="52" t="str">
+        <x:v>11978119870</x:v>
+      </x:c>
+      <x:c r="I28" s="56" t="str">
+        <x:v>WILD BADGER POWER Garden Tiller 53cc Mini Cultivator 15-inch.</x:v>
+      </x:c>
+      <x:c r="J28" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/Garden-Tiller-53cc-Mini-Cultivator-15-inch-Powerful-Liftable-Booster-Rod-Tilling-Tool-for-Lawn-Garden-and-Field-Soil-Cultivation/11978119870</x:v>
+      </x:c>
+      <x:c r="K28" s="51" t="str"/>
+      <x:c r="L28" s="51" t="str"/>
+      <x:c r="M28" s="51" t="str"/>
+      <x:c r="N28" s="52" t="str"/>
+      <x:c r="O28" s="51" t="str"/>
+      <x:c r="P28" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q28" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R28" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S28" s="51" t="str"/>
+      <x:c r="T28" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="N29" s="29"/>
+      <x:c r="A29" s="59" t="str">
+        <x:v>WALMART_WB20V16LM</x:v>
+      </x:c>
+      <x:c r="B29" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C29" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D29" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E29" s="51" t="str">
+        <x:v>Lawn Mower</x:v>
+      </x:c>
+      <x:c r="F29" s="52" t="str">
+        <x:v>WB20V16LM</x:v>
+      </x:c>
+      <x:c r="G29" s="52" t="str"/>
+      <x:c r="H29" s="52" t="str">
+        <x:v>13660751856</x:v>
+      </x:c>
+      <x:c r="I29" s="56" t="str">
+        <x:v>Wild Badger Power 40V 16″ Cordless Lawn Mower Brushless, 1,900 sq ft/0.044 ac,1×4.0Ah Battery &amp; Fast Charger,  5-Position Height,for Small Residential Lawns</x:v>
+      </x:c>
+      <x:c r="J29" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/WILD-BADGER-POWER-40V-16-Cordless-Brushless-Lawn-Mower-5-Cutting-Height-Adjustments-Electric-Quickly-Folding-Within-5-s-20V-2-4-0AH-Battery-Super-Cha/13660751856</x:v>
+      </x:c>
+      <x:c r="K29" s="51" t="str"/>
+      <x:c r="L29" s="51" t="str"/>
+      <x:c r="M29" s="51" t="str"/>
+      <x:c r="N29" s="52" t="str"/>
+      <x:c r="O29" s="51" t="str"/>
+      <x:c r="P29" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q29" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R29" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S29" s="51" t="str"/>
+      <x:c r="T29" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
-      <x:c r="N30" s="29"/>
+      <x:c r="A30" s="59" t="str">
+        <x:v>WALMART_WB40V18PLM</x:v>
+      </x:c>
+      <x:c r="B30" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C30" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D30" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E30" s="51" t="str">
+        <x:v>Lawn Mower</x:v>
+      </x:c>
+      <x:c r="F30" s="52" t="str">
+        <x:v>WB40V18PLM</x:v>
+      </x:c>
+      <x:c r="G30" s="52" t="str"/>
+      <x:c r="H30" s="52" t="str">
+        <x:v>5319348630</x:v>
+      </x:c>
+      <x:c r="I30" s="56" t="str">
+        <x:v>Wild Badger Power 40V 18″ Cordless Lawn Mower Brushless , 2,100 sq ft/0.048 ac, 1×4.0Ah Battery &amp; Fast Charger, 5-Position Height ,for Small-to-Medium Lawns</x:v>
+      </x:c>
+      <x:c r="J30" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/WILD-BADGER-POWER-40V-Lawn-Mower-Brushless-18-Cordless-5-Cutting-Height-Quikly-Folding/5319348630</x:v>
+      </x:c>
+      <x:c r="K30" s="51" t="str"/>
+      <x:c r="L30" s="51" t="str"/>
+      <x:c r="M30" s="51" t="str"/>
+      <x:c r="N30" s="52" t="str"/>
+      <x:c r="O30" s="51" t="str"/>
+      <x:c r="P30" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q30" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R30" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S30" s="51" t="str"/>
+      <x:c r="T30" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
-      <x:c r="N31" s="29"/>
+      <x:c r="A31" s="59" t="str">
+        <x:v>WALMART_WB40V14PLM</x:v>
+      </x:c>
+      <x:c r="B31" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C31" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D31" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E31" s="51" t="str">
+        <x:v>Lawn Mower</x:v>
+      </x:c>
+      <x:c r="F31" s="52" t="str">
+        <x:v>WB40V14PLM</x:v>
+      </x:c>
+      <x:c r="G31" s="52" t="str"/>
+      <x:c r="H31" s="52" t="str">
+        <x:v>16163460696</x:v>
+      </x:c>
+      <x:c r="I31" s="56" t="str">
+        <x:v>Wild Badger Power 40V 14″ Cordless Lawn Mower Brushless,1,600 sq ft/0.037 ac,1×4.0Ah Battery &amp; Fast Charger, 5-Position Height,for Townhomes &amp; Small Yards</x:v>
+      </x:c>
+      <x:c r="J31" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/Electric-Lawn-Mower-40V-Brushless-14-Cordless-Push-5-Cutting-Height-Adjustment-4Ah-Battery-and-Super-Charger-Blue/16163460696</x:v>
+      </x:c>
+      <x:c r="K31" s="51" t="str"/>
+      <x:c r="L31" s="51" t="str"/>
+      <x:c r="M31" s="51" t="str"/>
+      <x:c r="N31" s="52" t="str"/>
+      <x:c r="O31" s="51" t="str"/>
+      <x:c r="P31" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q31" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R31" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S31" s="51" t="str"/>
+      <x:c r="T31" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
-      <x:c r="N32" s="29"/>
+      <x:c r="A32" s="59" t="str">
+        <x:v>WALMART_SKRMX5</x:v>
+      </x:c>
+      <x:c r="B32" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C32" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D32" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E32" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F32" s="52" t="str">
+        <x:v>SKRMX5</x:v>
+      </x:c>
+      <x:c r="G32" s="52" t="str">
+        <x:v>X5</x:v>
+      </x:c>
+      <x:c r="H32" s="52" t="str">
+        <x:v>20278412919</x:v>
+      </x:c>
+      <x:c r="I32" s="56" t="str">
+        <x:v>Sunseeker X5 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J32" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/Sunseeker-X5-AWD-Robot-Lawn-Mower-0-5-Acre-21-780-Sq-Ft-Wireless-No-Boundary-Wire-Mower-RTK-Vision-Navigation-AI-Obstacle-Avoidance-App-Control/20278412919</x:v>
+      </x:c>
+      <x:c r="K32" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L32" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M32" s="51" t="str"/>
+      <x:c r="N32" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O32" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P32" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q32" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R32" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S32" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T32" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="N33" s="29"/>
+      <x:c r="A33" s="59" t="str">
+        <x:v>WALMART_SKRMX3PLUS</x:v>
+      </x:c>
+      <x:c r="B33" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C33" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D33" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E33" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F33" s="52" t="str">
+        <x:v>SKRMX3PLUS</x:v>
+      </x:c>
+      <x:c r="G33" s="52" t="str">
+        <x:v>X3PLUS</x:v>
+      </x:c>
+      <x:c r="H33" s="52" t="str">
+        <x:v>16987612478</x:v>
+      </x:c>
+      <x:c r="I33" s="56" t="str">
+        <x:v>Sunseeker X3PLUS Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J33" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/Sunseeker-X3-Plus-Robot-Lawn-Mower-Wire-0-3-Acre-13-000-Sq-Ft-Smart-APP-Control-AI-RTK-Navigation-6-Muti-Zone-Path-Planning-Small-Medium-Yards/16987612478</x:v>
+      </x:c>
+      <x:c r="K33" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L33" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M33" s="51" t="str"/>
+      <x:c r="N33" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O33" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P33" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q33" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R33" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S33" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T33" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="N34" s="29"/>
+      <x:c r="A34" s="59" t="str">
+        <x:v>WALMART_ORIONX7</x:v>
+      </x:c>
+      <x:c r="B34" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C34" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D34" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E34" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F34" s="52" t="str">
+        <x:v>ORIONX7</x:v>
+      </x:c>
+      <x:c r="G34" s="52" t="str">
+        <x:v>X7</x:v>
+      </x:c>
+      <x:c r="H34" s="52" t="str">
+        <x:v>17817006072</x:v>
+      </x:c>
+      <x:c r="I34" s="56" t="str">
+        <x:v>Sunseeker X7 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J34" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/SUNSEEKER-X7-Wireless-Robot-Lawn-Mower-0-75-Acre-32-000Sq-Ft-Smart-APP-Control-Vision-AI-System-RTK-Path-Planning-Adaptive-Floating-Cut-Height-4-Medi/17817006072</x:v>
+      </x:c>
+      <x:c r="K34" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L34" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M34" s="51" t="str"/>
+      <x:c r="N34" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O34" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P34" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q34" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R34" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S34" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T34" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="N35" s="29"/>
+      <x:c r="A35" s="59" t="str">
+        <x:v>WALMART_SKRMS4</x:v>
+      </x:c>
+      <x:c r="B35" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C35" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D35" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E35" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F35" s="52" t="str">
+        <x:v>SKRMS4</x:v>
+      </x:c>
+      <x:c r="G35" s="52" t="str">
+        <x:v>S4</x:v>
+      </x:c>
+      <x:c r="H35" s="52" t="str">
+        <x:v>20023610713</x:v>
+      </x:c>
+      <x:c r="I35" s="56" t="str">
+        <x:v>Sunseeker S4 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J35" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/Sunseeker-S4-LiDAR-Robot-Lawn-Mower-Up-0-25-Acre-1000-m-Vision-AI-360-3D-Navigation-Wire-Free-Virtual-Boundary-Systematic-Cutting-42-Slope-App-Contro/20023610713</x:v>
+      </x:c>
+      <x:c r="K35" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L35" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M35" s="51" t="str"/>
+      <x:c r="N35" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O35" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P35" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q35" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R35" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S35" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T35" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="N36" s="29"/>
+      <x:c r="A36" s="59" t="str">
+        <x:v>WALMART_SKRMV3</x:v>
+      </x:c>
+      <x:c r="B36" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C36" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D36" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="E36" s="51" t="str">
+        <x:v>ROBOTIC</x:v>
+      </x:c>
+      <x:c r="F36" s="52" t="str">
+        <x:v>SKRMV3</x:v>
+      </x:c>
+      <x:c r="G36" s="52" t="str">
+        <x:v>V3</x:v>
+      </x:c>
+      <x:c r="H36" s="52" t="str">
+        <x:v>15497122464</x:v>
+      </x:c>
+      <x:c r="I36" s="56" t="str">
+        <x:v>Sunseeker V3 Robotic Lawn Mower</x:v>
+      </x:c>
+      <x:c r="J36" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/SUNSEEKER-V3-Wireless-Robot-Lawn-Mower-0-15-Acre-6-400-Sq-Ft-Vision-AI-Automatic-Mower-One-Click-Mow-Smart-Obstacle-Avoidance-Multi-Zone-Navigation-2/15497122464</x:v>
+      </x:c>
+      <x:c r="K36" s="51" t="str">
+        <x:v>robot lawn mower</x:v>
+      </x:c>
+      <x:c r="L36" s="51" t="str">
+        <x:v>robotic lawn mower</x:v>
+      </x:c>
+      <x:c r="M36" s="51" t="str"/>
+      <x:c r="N36" s="52" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="O36" s="51" t="str">
+        <x:v>Sunseeker</x:v>
+      </x:c>
+      <x:c r="P36" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="Q36" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="R36" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S36" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="T36" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="N37" s="29"/>
+      <x:c r="A37" s="59" t="str">
+        <x:v>WALMART_WB20VTAB</x:v>
+      </x:c>
+      <x:c r="B37" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C37" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D37" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E37" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F37" s="52" t="str">
+        <x:v>WB20VTAB</x:v>
+      </x:c>
+      <x:c r="G37" s="52" t="str"/>
+      <x:c r="H37" s="52" t="str">
+        <x:v>864525478</x:v>
+      </x:c>
+      <x:c r="I37" s="56" t="str">
+        <x:v>Wild Badger Power 20V Weed Eater &amp; Trimmer Set, 2×2.0Ah Batteries, Cordless Lightweight Grass Trimmer for Small Yards, Fence Lines &amp; Easy Lawn Care</x:v>
+      </x:c>
+      <x:c r="J37" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/WILD-BADGER-POWER-20V-Cordless-String-Trimmer-With-blower-Combo-Set-Weed-Eater-Leaf-Blower/864525478</x:v>
+      </x:c>
+      <x:c r="K37" s="51" t="str"/>
+      <x:c r="L37" s="51" t="str"/>
+      <x:c r="M37" s="51" t="str"/>
+      <x:c r="N37" s="52" t="str"/>
+      <x:c r="O37" s="51" t="str"/>
+      <x:c r="P37" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q37" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R37" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S37" s="51" t="str"/>
+      <x:c r="T37" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="N38" s="29"/>
+      <x:c r="A38" s="59" t="str">
+        <x:v>WALMART_WB20VCOMBODP</x:v>
+      </x:c>
+      <x:c r="B38" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C38" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D38" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E38" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F38" s="52" t="str">
+        <x:v>WB20VCOMBODP</x:v>
+      </x:c>
+      <x:c r="G38" s="52" t="str"/>
+      <x:c r="H38" s="52" t="str">
+        <x:v>16104323450</x:v>
+      </x:c>
+      <x:c r="I38" s="56" t="str">
+        <x:v>Wild Badger 40V Cordless String Trimmer with Pole Saw, Hedge Trimmer &amp; Brush Cutter Attachments, 4-Tool Kit, 2 Batteries &amp; Charger Included</x:v>
+      </x:c>
+      <x:c r="J38" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/40V-Cordless-Weed-Wacker-String-Trimmer-Edger-Hedge-Trimmer-Brush-Cutter-Blade-Pole-Saw-Attachment-Capable-4-in-1-Multi-Tool-Kit-2-20V-4Ah-Battery-1/16104323450</x:v>
+      </x:c>
+      <x:c r="K38" s="51" t="str"/>
+      <x:c r="L38" s="51" t="str"/>
+      <x:c r="M38" s="51" t="str"/>
+      <x:c r="N38" s="52" t="str"/>
+      <x:c r="O38" s="51" t="str"/>
+      <x:c r="P38" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q38" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R38" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S38" s="51" t="str"/>
+      <x:c r="T38" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="N39" s="29"/>
+      <x:c r="A39" s="59" t="str">
+        <x:v>WALMART_WB40VCOMBO</x:v>
+      </x:c>
+      <x:c r="B39" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C39" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D39" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E39" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F39" s="52" t="str">
+        <x:v>WB40VCOMBO</x:v>
+      </x:c>
+      <x:c r="G39" s="52" t="str"/>
+      <x:c r="H39" s="52" t="str">
+        <x:v>17598657653</x:v>
+      </x:c>
+      <x:c r="I39" s="56" t="str">
+        <x:v>Wild Badger 40V 4-in-1 Cordless Outdoor Power Tool Kit (Weed Wacker, Pole Saw, Hedge Trimmer, Brush Cutter) with 2*4 AhBatteries &amp; Charger</x:v>
+      </x:c>
+      <x:c r="J39" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/Wild-Badger-Power-40V-Cordless-Weed-Wacker-String-Trimmer-Edger-Hedge-Trimmer-Brush-Cutter-Blade-Pole-Saw-Attachment-Capable-4-in-1-Multi-Tool-Kit-2/17598657653</x:v>
+      </x:c>
+      <x:c r="K39" s="51" t="str"/>
+      <x:c r="L39" s="51" t="str"/>
+      <x:c r="M39" s="51" t="str"/>
+      <x:c r="N39" s="52" t="str"/>
+      <x:c r="O39" s="51" t="str"/>
+      <x:c r="P39" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q39" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R39" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S39" s="51" t="str"/>
+      <x:c r="T39" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="N40" s="29"/>
+      <x:c r="A40" s="59" t="str">
+        <x:v>WALMART_WBPMT26P</x:v>
+      </x:c>
+      <x:c r="B40" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C40" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D40" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E40" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F40" s="52" t="str">
+        <x:v>WBPMT26P</x:v>
+      </x:c>
+      <x:c r="G40" s="52" t="str"/>
+      <x:c r="H40" s="52" t="str">
+        <x:v>838770895</x:v>
+      </x:c>
+      <x:c r="I40" s="56" t="str">
+        <x:v>WILD BADGER POWER 26cc Multi -Tool Gas String Trimmer 4 in 1 Garden Tool Combo with hedge pole saw</x:v>
+      </x:c>
+      <x:c r="J40" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/WILD-BADGER-POWER-26cc-Multi-Tool-Trimmer-4-in-1-Garden-Tool-Combo-with-hedge-pole-saw/838770895</x:v>
+      </x:c>
+      <x:c r="K40" s="51" t="str"/>
+      <x:c r="L40" s="51" t="str"/>
+      <x:c r="M40" s="51" t="str"/>
+      <x:c r="N40" s="52" t="str"/>
+      <x:c r="O40" s="51" t="str"/>
+      <x:c r="P40" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q40" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R40" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S40" s="51" t="str"/>
+      <x:c r="T40" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="N41" s="29"/>
+      <x:c r="A41" s="59" t="str">
+        <x:v>WALMART_WB26MTSE</x:v>
+      </x:c>
+      <x:c r="B41" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C41" s="51" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D41" s="51" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E41" s="51" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F41" s="52" t="str">
+        <x:v>WB26MTSE</x:v>
+      </x:c>
+      <x:c r="G41" s="52" t="str"/>
+      <x:c r="H41" s="52" t="str">
+        <x:v>1856935316</x:v>
+      </x:c>
+      <x:c r="I41" s="56" t="str">
+        <x:v>WILD BADGER POWER Gas 4-in-1 Yard Care System, 26cc 2-Cycle Full-Crankshaft Engine Multi-Tool with Attachments, String Trimmer/Edger, Hedge Trimmer and Brush Cutter Blade</x:v>
+      </x:c>
+      <x:c r="J41" s="62" t="str">
+        <x:v>http://www.walmart.com/ip/WILD-BADGER-POWER-Gas-4-in-1-Yard-Care-System-26cc-2-Cycle-Full-Crankshaft-Engine-Multi-Tool-Attachments-String-Trimmer-Edger-Hedge-Trimmer-Brush-Cut/1856935316</x:v>
+      </x:c>
+      <x:c r="K41" s="51" t="str"/>
+      <x:c r="L41" s="51" t="str"/>
+      <x:c r="M41" s="51" t="str"/>
+      <x:c r="N41" s="52" t="str"/>
+      <x:c r="O41" s="51" t="str"/>
+      <x:c r="P41" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q41" s="51" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R41" s="51" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S41" s="51" t="str"/>
+      <x:c r="T41" s="62" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="N42" s="29"/>
+      <x:c r="A42" s="60" t="str">
+        <x:v>WALMART_WB40VTBCC</x:v>
+      </x:c>
+      <x:c r="B42" s="54" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="C42" s="54" t="str">
+        <x:v>WALMART</x:v>
+      </x:c>
+      <x:c r="D42" s="54" t="str">
+        <x:v>WILD BADGER POWER</x:v>
+      </x:c>
+      <x:c r="E42" s="54" t="str">
+        <x:v>String Trimmer</x:v>
+      </x:c>
+      <x:c r="F42" s="55" t="str">
+        <x:v>WB40VTBCC</x:v>
+      </x:c>
+      <x:c r="G42" s="55" t="str"/>
+      <x:c r="H42" s="55" t="str">
+        <x:v>3962878922</x:v>
+      </x:c>
+      <x:c r="I42" s="57" t="str">
+        <x:v>WILD BADGER POWER 40V Weed Wacker &amp; Leaf Blower, Wheeled Edger Kit Electric with 2Ah Battery &amp; Charger, String Trimmer</x:v>
+      </x:c>
+      <x:c r="J42" s="63" t="str">
+        <x:v>http://www.walmart.com/ip/Wild-Badger-Power-Cordless-40-Volt-Brushed-Trimmer-and-Brushed-Blower-Combo-Includes-2-0-Ah-Battery-and-Clip-on-Charger/3962878922</x:v>
+      </x:c>
+      <x:c r="K42" s="54" t="str"/>
+      <x:c r="L42" s="54" t="str"/>
+      <x:c r="M42" s="54" t="str"/>
+      <x:c r="N42" s="55" t="str"/>
+      <x:c r="O42" s="54" t="str"/>
+      <x:c r="P42" s="54" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="Q42" s="54" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="R42" s="54" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
+      <x:c r="S42" s="54" t="str"/>
+      <x:c r="T42" s="63" t="str">
+        <x:v>Review scope promoted from successful frozen run 2026-08-06 under explicit user authorization on 2026-08-12.</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="N43" s="29"/>
@@ -1188,7 +3312,7 @@
       <x:c r="N201" s="29"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="4">
+  <x:dataValidations count="9">
     <x:dataValidation type="list" sqref="B2:B201">
       <x:formula1>"TRUE,FALSE"</x:formula1>
     </x:dataValidation>
@@ -1200,6 +3324,21 @@
     </x:dataValidation>
     <x:dataValidation type="whole" operator="greaterThan" sqref="S2:S201">
       <x:formula1>0</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="B2:B42">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C42">
+      <x:formula1>"WALMART,THD,LOWES"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="P2:P42">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="Q2:Q42">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="R2:R42">
+      <x:formula1>"TRUE,FALSE"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
